--- a/survey_templates/041_math_interest_survey--survey_templates.xlsx
+++ b/survey_templates/041_math_interest_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1075,7 +1075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:C50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'algebra':_'a_comprehensive_introduction_to_the_theory_of_numbers'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'Algebra': 'A Comprehensive Introduction to the Theory of Numbers'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1346,12 +1346,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'calculus':_'early_indicators'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'Calculus': 'Early Indicators'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>3blue1blue</t>
+          <t>khan_academy</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>3Blue1Blue</t>
+          <t>Khan Academy</t>
         </is>
       </c>
     </row>
@@ -1924,27 +1924,10 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>khan_academy</t>
+          <t>ted-ed</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
-        <is>
-          <t>Khan Academy</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>favorite_educational_video_choices</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>ted-ed</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
         <is>
           <t>TED-Ed</t>
         </is>
